--- a/data/trans_camb/KIDM_C_3_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 17,82</t>
+          <t>-0,18; 16,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 14,4</t>
+          <t>-4,61; 13,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -1,32</t>
+          <t>-10,77; -0,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 19,21</t>
+          <t>-1,98; 17,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 26,55</t>
+          <t>3,97; 25,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -1,11</t>
+          <t>-10,62; -1,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 14,57</t>
+          <t>1,25; 14,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 16,63</t>
+          <t>1,78; 16,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -1,36</t>
+          <t>-8,83; -1,39</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,13; —</t>
+          <t>-34,92; 1077,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,89; —</t>
+          <t>-63,02; 1226,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,74; —</t>
+          <t>-3,54; 1932,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 711,59</t>
+          <t>5,48; 763,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 978,45</t>
+          <t>4,63; 829,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 17,3</t>
+          <t>6,74; 17,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,15</t>
+          <t>-0,42; 7,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 3,58</t>
+          <t>-5,13; 3,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 12,11</t>
+          <t>3,82; 11,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,51</t>
+          <t>1,75; 9,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 1,12</t>
+          <t>-4,46; 1,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,31</t>
+          <t>6,59; 13,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,78</t>
+          <t>1,57; 7,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,92</t>
+          <t>-3,71; 1,18</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,02; 446,79</t>
+          <t>82,49; 457,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 195,58</t>
+          <t>-7,36; 181,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,33; 92,03</t>
+          <t>-64,74; 84,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,91; 436,9</t>
+          <t>52,18; 451,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,83; 329,54</t>
+          <t>19,21; 333,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,06; 49,5</t>
+          <t>-81,44; 56,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,73; 359,77</t>
+          <t>104,66; 352,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,41; 182,43</t>
+          <t>22,28; 195,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 28,82</t>
+          <t>-60,55; 35,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 12,77</t>
+          <t>-3,28; 12,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 13,43</t>
+          <t>-2,89; 12,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,07; -1,35</t>
+          <t>-12,65; -1,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 17,12</t>
+          <t>-0,66; 16,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 11,49</t>
+          <t>-2,08; 11,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 1,13</t>
+          <t>-9,59; 1,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 11,95</t>
+          <t>0,72; 12,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 10,24</t>
+          <t>-0,33; 10,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -0,62</t>
+          <t>-8,5; -0,89</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,86; 640,21</t>
+          <t>-52,02; 626,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 844,6</t>
+          <t>-42,98; 642,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 1424,41</t>
+          <t>-40,4; 1208,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 888,71</t>
+          <t>-52,41; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 556,26</t>
+          <t>-5,12; 529,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 384,77</t>
+          <t>-16,88; 404,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,81</t>
+          <t>-100,0; 128,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 13,84</t>
+          <t>5,73; 14,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,06</t>
+          <t>0,07; 6,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,59</t>
+          <t>-4,67; 1,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 11,2</t>
+          <t>4,41; 10,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 9,44</t>
+          <t>2,93; 9,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,24</t>
+          <t>-4,45; 0,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 11,18</t>
+          <t>6,32; 11,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,24</t>
+          <t>2,67; 7,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,14</t>
+          <t>-3,81; -0,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>74,14; 337,35</t>
+          <t>76,44; 371,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,81; 178,07</t>
+          <t>0,07; 172,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,18; 42,34</t>
+          <t>-69,66; 54,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77,78; 391,32</t>
+          <t>76,31; 381,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,93; 331,01</t>
+          <t>51,34; 318,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,65; 15,25</t>
+          <t>-83,69; 18,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>102,56; 295,18</t>
+          <t>107,26; 303,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,07; 190,47</t>
+          <t>49,16; 186,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,57; -2,86</t>
+          <t>-68,43; 0,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/KIDM_C_3_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 16,2</t>
+          <t>-0,45; 16,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 13,89</t>
+          <t>-4,05; 14,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -0,76</t>
+          <t>-10,8; -1,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 17,12</t>
+          <t>-1,73; 16,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 25,92</t>
+          <t>2,98; 28,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,62; -1,12</t>
+          <t>-10,89; -1,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 14,33</t>
+          <t>1,74; 14,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 16,67</t>
+          <t>2,0; 16,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -1,39</t>
+          <t>-8,31; -1,41</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 1077,93</t>
+          <t>-21,69; 1076,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-63,02; 1226,13</t>
+          <t>-63,63; 1137,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1932,49</t>
+          <t>-17,9; 1803,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 763,56</t>
+          <t>10,11; 691,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 829,95</t>
+          <t>15,03; 1157,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 17,45</t>
+          <t>7,09; 17,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,38</t>
+          <t>-0,6; 7,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,35</t>
+          <t>-4,85; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 11,96</t>
+          <t>3,7; 11,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 9,12</t>
+          <t>1,16; 9,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,19</t>
+          <t>-4,89; 0,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,04</t>
+          <t>6,72; 13,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,16</t>
+          <t>1,88; 7,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,18</t>
+          <t>-3,75; 0,98</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,49; 457,35</t>
+          <t>87,8; 442,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 181,17</t>
+          <t>-9,75; 217,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,74; 84,94</t>
+          <t>-66,93; 74,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,18; 451,07</t>
+          <t>62,84; 486,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,21; 333,04</t>
+          <t>14,57; 358,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,44; 56,93</t>
+          <t>-83,34; 51,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>104,66; 352,54</t>
+          <t>107,66; 351,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,28; 195,55</t>
+          <t>26,86; 206,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,55; 35,87</t>
+          <t>-61,62; 27,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 12,53</t>
+          <t>-3,15; 12,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 12,9</t>
+          <t>-2,97; 13,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,65; -1,3</t>
+          <t>-13,08; -1,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 16,43</t>
+          <t>0,23; 16,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 11,57</t>
+          <t>-2,73; 11,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 1,15</t>
+          <t>-9,39; 1,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 12,22</t>
+          <t>0,48; 11,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 10,46</t>
+          <t>-0,27; 10,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,5; -0,89</t>
+          <t>-8,26; -0,71</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,02; 626,07</t>
+          <t>-46,93; 779,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 642,09</t>
+          <t>-43,77; 717,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 1208,03</t>
+          <t>-21,47; 1267,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,41; —</t>
+          <t>-54,57; 1101,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 529,87</t>
+          <t>-5,96; 503,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 404,55</t>
+          <t>-12,04; 498,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 128,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 14,1</t>
+          <t>6,09; 13,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,93</t>
+          <t>0,29; 7,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,92</t>
+          <t>-4,77; 1,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,81</t>
+          <t>4,04; 11,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,14</t>
+          <t>2,88; 9,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,2</t>
+          <t>-4,44; 0,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,51</t>
+          <t>6,02; 11,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,25</t>
+          <t>2,42; 7,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,08</t>
+          <t>-3,98; 0,02</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>76,44; 371,89</t>
+          <t>83,17; 370,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 172,09</t>
+          <t>3,71; 191,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 54,38</t>
+          <t>-70,81; 51,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,31; 381,76</t>
+          <t>72,29; 394,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,34; 318,32</t>
+          <t>51,27; 320,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,69; 18,19</t>
+          <t>-83,33; 17,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>107,26; 303,67</t>
+          <t>101,83; 290,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,16; 186,77</t>
+          <t>38,93; 186,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 0,61</t>
+          <t>-69,97; 1,1</t>
         </is>
       </c>
     </row>
